--- a/amostras/principal/P26/matriz_rastreabilidade_P26.xlsx
+++ b/amostras/principal/P26/matriz_rastreabilidade_P26.xlsx
@@ -694,6 +694,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -751,6 +752,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -808,6 +810,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -865,6 +868,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -922,6 +926,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1039,6 +1044,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1096,6 +1102,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1153,6 +1160,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1210,6 +1218,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1267,6 +1276,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1324,6 +1334,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1381,6 +1392,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1438,6 +1450,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Nenhum</t>
@@ -1495,6 +1508,7 @@
           <t>Nenhuma</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Nenhum</t>
